--- a/engine_package/Res/MuDataEditor/天使之战_v1.0.0.0/Out/cfg_privilege.xlsx
+++ b/engine_package/Res/MuDataEditor/天使之战_v1.0.0.0/Out/cfg_privilege.xlsx
@@ -184,7 +184,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="25">
+  <fonts count="24">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -200,12 +200,6 @@
     </font>
     <font>
       <sz val="11"/>
-      <name val="微软雅黑"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="微软雅黑"/>
       <charset val="134"/>
     </font>
@@ -696,137 +690,137 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -854,19 +848,16 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1178,7 +1169,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:M35"/>
+  <dimension ref="A1:M34"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="8" style="2" customWidth="1"/>
@@ -1352,9 +1343,9 @@
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="2">
-        <v>72</v>
-      </c>
-      <c r="B5" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="B5" s="3" t="s">
         <v>39</v>
       </c>
       <c r="C5" s="3">
@@ -1363,7 +1354,7 @@
       <c r="D5" s="3">
         <v>12</v>
       </c>
-      <c r="E5" s="10">
+      <c r="E5" s="9">
         <v>30031062</v>
       </c>
       <c r="F5" s="2">
@@ -1372,15 +1363,15 @@
       <c r="G5" s="2">
         <v>43200</v>
       </c>
-      <c r="H5" s="9" t="s">
+      <c r="H5" s="3" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="6" spans="1:13">
       <c r="A6" s="2">
-        <v>73</v>
-      </c>
-      <c r="B6" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="B6" s="10" t="s">
         <v>41</v>
       </c>
       <c r="C6" s="3">
@@ -1389,16 +1380,16 @@
       <c r="D6" s="3">
         <v>12</v>
       </c>
-      <c r="E6" s="10">
+      <c r="E6" s="9">
         <v>30031063</v>
       </c>
       <c r="F6" s="2">
         <v>30000014</v>
       </c>
       <c r="G6" s="2">
-        <v>1440</v>
-      </c>
-      <c r="H6" s="9" t="s">
+        <v>43200</v>
+      </c>
+      <c r="H6" s="3" t="s">
         <v>42</v>
       </c>
     </row>
@@ -1406,7 +1397,7 @@
       <c r="A7" s="2">
         <v>74</v>
       </c>
-      <c r="B7" s="11" t="s">
+      <c r="B7" s="10" t="s">
         <v>43</v>
       </c>
       <c r="C7" s="3">
@@ -1415,7 +1406,7 @@
       <c r="D7" s="3">
         <v>12</v>
       </c>
-      <c r="E7" s="10">
+      <c r="E7" s="9">
         <v>30031064</v>
       </c>
       <c r="F7" s="2">
@@ -1424,108 +1415,104 @@
       <c r="G7" s="2">
         <v>43200</v>
       </c>
-      <c r="H7" s="9" t="s">
+      <c r="H7" s="3" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="8" spans="1:13">
-      <c r="G8" s="12"/>
-      <c r="I8" s="8"/>
+      <c r="G8" s="11"/>
     </row>
     <row r="9" spans="1:13">
-      <c r="G9" s="12"/>
+      <c r="G9" s="11"/>
     </row>
     <row r="10" spans="1:13">
-      <c r="G10" s="12"/>
+      <c r="G10" s="11"/>
     </row>
     <row r="11" spans="1:13">
-      <c r="G11" s="12"/>
+      <c r="G11" s="11"/>
     </row>
     <row r="12" spans="1:13">
-      <c r="G12" s="12"/>
+      <c r="G12" s="11"/>
     </row>
     <row r="13" spans="1:13">
-      <c r="G13" s="12"/>
+      <c r="G13" s="11"/>
     </row>
     <row r="14" spans="1:13">
-      <c r="G14" s="12"/>
+      <c r="G14" s="11"/>
     </row>
     <row r="15" spans="1:13">
-      <c r="G15" s="12"/>
+      <c r="G15" s="11"/>
     </row>
     <row r="16" spans="1:13">
-      <c r="G16" s="12"/>
+      <c r="G16" s="11"/>
     </row>
     <row r="17" spans="1:13">
-      <c r="G17" s="12"/>
+      <c r="G17" s="11"/>
     </row>
     <row r="18" spans="1:13">
-      <c r="G18" s="12"/>
+      <c r="G18" s="11"/>
     </row>
     <row r="19" spans="1:13">
-      <c r="G19" s="12"/>
+      <c r="G19" s="11"/>
     </row>
     <row r="20" spans="1:13">
-      <c r="G20" s="12"/>
-    </row>
-    <row r="21" spans="1:13">
-      <c r="G21" s="12"/>
-    </row>
-    <row r="22" ht="4" customHeight="1"/>
-    <row r="23" customFormat="1" spans="1:13">
-      <c r="A23" s="2"/>
-      <c r="B23" s="3"/>
-      <c r="C23" s="3"/>
-      <c r="D23" s="3"/>
-      <c r="E23" s="2"/>
-      <c r="F23" s="2"/>
-      <c r="G23" s="2"/>
-      <c r="I23" s="4"/>
-      <c r="J23" s="4"/>
-      <c r="K23" s="4"/>
-      <c r="L23" s="4"/>
-      <c r="M23" s="4"/>
+      <c r="G20" s="11"/>
+    </row>
+    <row r="21" ht="4" customHeight="1"/>
+    <row r="22" customFormat="1" spans="1:13">
+      <c r="A22" s="2"/>
+      <c r="B22" s="3"/>
+      <c r="C22" s="3"/>
+      <c r="D22" s="3"/>
+      <c r="E22" s="2"/>
+      <c r="F22" s="2"/>
+      <c r="G22" s="2"/>
+      <c r="I22" s="4"/>
+      <c r="J22" s="4"/>
+      <c r="K22" s="4"/>
+      <c r="L22" s="4"/>
+      <c r="M22" s="4"/>
+    </row>
+    <row r="23" spans="1:13">
+      <c r="B23" s="12"/>
+      <c r="G23" s="11"/>
     </row>
     <row r="24" spans="1:13">
-      <c r="B24" s="13"/>
-      <c r="G24" s="12"/>
+      <c r="B24" s="12"/>
     </row>
     <row r="25" spans="1:13">
-      <c r="B25" s="13"/>
+      <c r="B25" s="12"/>
+      <c r="G25" s="11"/>
     </row>
     <row r="26" spans="1:13">
-      <c r="B26" s="13"/>
-      <c r="G26" s="12"/>
+      <c r="B26" s="12"/>
     </row>
     <row r="27" spans="1:13">
-      <c r="B27" s="13"/>
+      <c r="B27" s="12"/>
+      <c r="G27" s="11"/>
     </row>
     <row r="28" spans="1:13">
-      <c r="B28" s="13"/>
-      <c r="G28" s="12"/>
+      <c r="B28" s="12"/>
     </row>
     <row r="29" spans="1:13">
-      <c r="B29" s="13"/>
+      <c r="B29" s="12"/>
+      <c r="G29" s="11"/>
     </row>
     <row r="30" spans="1:13">
-      <c r="B30" s="13"/>
-      <c r="G30" s="12"/>
+      <c r="B30" s="12"/>
     </row>
     <row r="31" spans="1:13">
-      <c r="B31" s="13"/>
+      <c r="B31" s="12"/>
+      <c r="G31" s="11"/>
     </row>
     <row r="32" spans="1:13">
-      <c r="B32" s="13"/>
-      <c r="G32" s="12"/>
-    </row>
-    <row r="33" spans="2:5">
-      <c r="B33" s="13"/>
-    </row>
-    <row r="34" spans="2:5">
-      <c r="E34" s="10"/>
-    </row>
-    <row r="35" spans="2:5">
-      <c r="E35" s="10"/>
+      <c r="B32" s="12"/>
+    </row>
+    <row r="33" spans="5:5">
+      <c r="E33" s="9"/>
+    </row>
+    <row r="34" spans="5:5">
+      <c r="E34" s="9"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/engine_package/Res/MuDataEditor/天使之战_v1.0.0.0/Out/cfg_privilege.xlsx
+++ b/engine_package/Res/MuDataEditor/天使之战_v1.0.0.0/Out/cfg_privilege.xlsx
@@ -1,10 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\天使之战\tszz_GMTest\engine_package\Res\MuDataEditor\天使之战_v1.0.0.0\Out\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12255"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -29,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="45">
   <si>
     <t>序列</t>
   </si>
@@ -162,16 +167,19 @@
     <t>畅玩卡</t>
   </si>
   <si>
-    <t>24#23#2#13#17#16#25#6#18#28</t>
+    <t>24#23#2#13#25#6#18#17</t>
   </si>
   <si>
     <t>黄金卡(1天)</t>
   </si>
   <si>
-    <t>18#28</t>
-  </si>
-  <si>
     <t>黄金卡(30天)</t>
+  </si>
+  <si>
+    <t>强化天使</t>
+  </si>
+  <si>
+    <t>强化恶魔</t>
   </si>
 </sst>
 </file>
@@ -820,7 +828,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -853,6 +861,12 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
@@ -910,6 +924,25 @@
     <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
     <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
+  <dxfs count="2">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFF9900"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -1389,8 +1422,8 @@
       <c r="G6" s="2">
         <v>43200</v>
       </c>
-      <c r="H6" s="3" t="s">
-        <v>42</v>
+      <c r="H6" s="3">
+        <v>18</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -1398,7 +1431,7 @@
         <v>74</v>
       </c>
       <c r="B7" s="10" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C7" s="3">
         <v>2</v>
@@ -1415,48 +1448,98 @@
       <c r="G7" s="2">
         <v>43200</v>
       </c>
-      <c r="H7" s="3" t="s">
-        <v>42</v>
+      <c r="H7" s="3">
+        <v>18</v>
       </c>
     </row>
     <row r="8" spans="1:13">
-      <c r="G8" s="11"/>
+      <c r="A8" s="2">
+        <v>100</v>
+      </c>
+      <c r="B8" s="11" t="s">
+        <v>43</v>
+      </c>
+      <c r="C8" s="3">
+        <v>2</v>
+      </c>
+      <c r="D8" s="3">
+        <v>12</v>
+      </c>
+      <c r="E8" s="12">
+        <v>2140000899</v>
+      </c>
+      <c r="F8" s="2">
+        <v>30000015</v>
+      </c>
+      <c r="G8" s="2">
+        <v>43200</v>
+      </c>
+      <c r="H8" s="3">
+        <v>16</v>
+      </c>
     </row>
     <row r="9" spans="1:13">
-      <c r="G9" s="11"/>
+      <c r="A9" s="2">
+        <v>101</v>
+      </c>
+      <c r="B9" s="12" t="s">
+        <v>44</v>
+      </c>
+      <c r="C9" s="3">
+        <v>2</v>
+      </c>
+      <c r="D9" s="3">
+        <v>12</v>
+      </c>
+      <c r="E9" s="12">
+        <v>2140000799</v>
+      </c>
+      <c r="F9" s="2">
+        <v>30000015</v>
+      </c>
+      <c r="G9" s="2">
+        <v>43200</v>
+      </c>
+      <c r="H9" s="3">
+        <v>16</v>
+      </c>
     </row>
     <row r="10" spans="1:13">
-      <c r="G10" s="11"/>
+      <c r="G10" s="13"/>
     </row>
     <row r="11" spans="1:13">
-      <c r="G11" s="11"/>
+      <c r="B11" s="12"/>
+      <c r="C11" s="11"/>
+      <c r="G11" s="13"/>
     </row>
     <row r="12" spans="1:13">
-      <c r="G12" s="11"/>
+      <c r="B12" s="12"/>
+      <c r="C12" s="12"/>
+      <c r="G12" s="13"/>
     </row>
     <row r="13" spans="1:13">
-      <c r="G13" s="11"/>
+      <c r="G13" s="13"/>
     </row>
     <row r="14" spans="1:13">
-      <c r="G14" s="11"/>
+      <c r="G14" s="13"/>
     </row>
     <row r="15" spans="1:13">
-      <c r="G15" s="11"/>
+      <c r="G15" s="13"/>
     </row>
     <row r="16" spans="1:13">
-      <c r="G16" s="11"/>
+      <c r="G16" s="13"/>
     </row>
     <row r="17" spans="1:13">
-      <c r="G17" s="11"/>
+      <c r="G17" s="13"/>
     </row>
     <row r="18" spans="1:13">
-      <c r="G18" s="11"/>
+      <c r="G18" s="13"/>
     </row>
     <row r="19" spans="1:13">
-      <c r="G19" s="11"/>
+      <c r="G19" s="13"/>
     </row>
     <row r="20" spans="1:13">
-      <c r="G20" s="11"/>
+      <c r="G20" s="13"/>
     </row>
     <row r="21" ht="4" customHeight="1"/>
     <row r="22" customFormat="1" spans="1:13">
@@ -1474,39 +1557,39 @@
       <c r="M22" s="4"/>
     </row>
     <row r="23" spans="1:13">
-      <c r="B23" s="12"/>
-      <c r="G23" s="11"/>
+      <c r="B23" s="14"/>
+      <c r="G23" s="13"/>
     </row>
     <row r="24" spans="1:13">
-      <c r="B24" s="12"/>
+      <c r="B24" s="14"/>
     </row>
     <row r="25" spans="1:13">
-      <c r="B25" s="12"/>
-      <c r="G25" s="11"/>
+      <c r="B25" s="14"/>
+      <c r="G25" s="13"/>
     </row>
     <row r="26" spans="1:13">
-      <c r="B26" s="12"/>
+      <c r="B26" s="14"/>
     </row>
     <row r="27" spans="1:13">
-      <c r="B27" s="12"/>
-      <c r="G27" s="11"/>
+      <c r="B27" s="14"/>
+      <c r="G27" s="13"/>
     </row>
     <row r="28" spans="1:13">
-      <c r="B28" s="12"/>
+      <c r="B28" s="14"/>
     </row>
     <row r="29" spans="1:13">
-      <c r="B29" s="12"/>
-      <c r="G29" s="11"/>
+      <c r="B29" s="14"/>
+      <c r="G29" s="13"/>
     </row>
     <row r="30" spans="1:13">
-      <c r="B30" s="12"/>
+      <c r="B30" s="14"/>
     </row>
     <row r="31" spans="1:13">
-      <c r="B31" s="12"/>
-      <c r="G31" s="11"/>
+      <c r="B31" s="14"/>
+      <c r="G31" s="13"/>
     </row>
     <row r="32" spans="1:13">
-      <c r="B32" s="12"/>
+      <c r="B32" s="14"/>
     </row>
     <row r="33" spans="5:5">
       <c r="E33" s="9"/>
@@ -1515,6 +1598,46 @@
       <c r="E34" s="9"/>
     </row>
   </sheetData>
+  <conditionalFormatting sqref="E8">
+    <cfRule type="duplicateValues" dxfId="0" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="2"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E9">
+    <cfRule type="duplicateValues" dxfId="0" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="1"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B11">
+    <cfRule type="duplicateValues" dxfId="0" priority="14"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="12"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B12">
+    <cfRule type="duplicateValues" dxfId="0" priority="13"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="11"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B8:B9">
+    <cfRule type="duplicateValues" dxfId="0" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="6"/>
+    <cfRule type="colorScale" priority="5">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FFFF7128"/>
+        <color rgb="FFFFEF9C"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C11:C12">
+    <cfRule type="duplicateValues" dxfId="0" priority="10"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="9"/>
+    <cfRule type="colorScale" priority="8">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FFFF7128"/>
+        <color rgb="FFFFEF9C"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
   <headerFooter/>
